--- a/报告/机构持仓决策报告.xlsx
+++ b/报告/机构持仓决策报告.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>未就绪：需先运行数据管道</t>
+          <t>可用：每期前 50 只持股基金数，共 65 只（两期并集）</t>
         </is>
       </c>
     </row>
@@ -2212,75 +2212,2881 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>项</t>
+          <t>股票名称</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>2026Q2 持股基金数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026Q3 持股基金数</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>持仓市值(亿)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2026Q2 持仓市值(亿)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Δ持股基金数</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Δ持仓市值(亿)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>榜单状态</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>所属行业</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>行业动作</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>分档结论</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>未就绪</t>
+          <t>长鑫科技</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="n">
+        <v>734</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>410.9141</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n">
+        <v>734</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>410.9141</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>原因</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>个股级持股基金数已取到前 50 只/期，但所属行业映射与个股次季收益缺失，无法完成 IC 验证，按规则不得进入决策表</t>
+          <t>药明康德</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>945</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>452.3</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>239.3487</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>472</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>212.9513</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>需要的数据</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>股票→申万一级映射（31 次行业成分查询）、个股季度收益（逐只查询）</t>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>608</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>218.2551</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>121.9496</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>96.30549999999999</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>有色金属</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>回避</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>当前可用</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>每期 50 只的 Δ持股基金数、Δ持仓市值（仅作观察）</t>
+          <t>药明生物</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>115.7169</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>115.7169</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>工商银行</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>40.01</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>松发股份</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>75.6947</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>75.6947</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>睿创微纳</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>78.3027</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>78.3027</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>牧原股份</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>58.2173</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>58.2173</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>凯莱英</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>85.514</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>85.514</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>康龙化成</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>93.1613</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>93.1613</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>联讯仪器</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>140.4678</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>140.4678</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>长江电力</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>30.1899</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30.1899</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>天孚通信</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>365</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>238.2326</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>159.703</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>78.52959999999999</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>中国海洋石油</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>74.23350000000001</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>74.23350000000001</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>信达生物</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>72.31440000000001</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>72.31440000000001</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>格力电器</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>40.3576</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>40.3576</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>建设银行</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>34.598</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>34.598</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>新宙邦</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>43.0062</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>43.0062</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>新进前50</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>招商银行</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>61.6203</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>44.3598</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>17.2605</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>宁波银行</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>77.5448</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>61.6887</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>15.8561</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>贵州茅台</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>440</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>508</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>169.6373</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>153.7982</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>15.8391</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>食品饮料</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>深南电路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>199.3336</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>208.6131</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>-9.279500000000013</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>沪电股份</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>268.3492</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>311.1592</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>-42.81</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>源杰科技</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>375</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>437</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>360.8732</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>459.8492</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>-98.976</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>美的集团</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>338</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>388</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>149.9868</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>123.4121</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>26.57469999999999</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>家用电器</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>阿里巴巴-W</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>77.7022</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>63.0564</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>14.64580000000001</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>腾讯控股</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>371</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>418</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>172.4157</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>151.8548</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>20.56089999999998</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>中国平安</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>59.6671</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>71.36960000000001</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>-11.70250000000001</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>芯碁微装</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>48.7481</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>55.0891</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>-6.341000000000001</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>生益科技</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>202.2786</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>303.7827</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>-101.5041</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>工业富联</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>202.229</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>223.7377</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>-21.50869999999998</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>中科飞测</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>181.2856</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>269.4167</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>-88.1311</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>芯源微</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>133.8083</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>159.8933</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>-26.08500000000001</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>拓荆科技</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>176.3516</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>229.9464</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>-53.59480000000002</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>三环集团</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>377</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>219.6952</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>331.8311</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-17</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>-112.1359</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>新易盛</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1123</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1070</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>861.1493</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1348.6344</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-53</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>-487.4850999999999</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>通信</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>恒瑞医药</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>102.2109</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>128.2716</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-78</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>-26.06070000000001</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>标配</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>长川科技</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>135.1987</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>237.0128</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-79</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>-101.8141</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>北方华创</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>562</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>474</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>266.7232</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>484.7615</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-88</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>-218.0383</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>67.71899999999999</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>103.733</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-88</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>-36.01400000000001</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>观察（行业未映射，不能分档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>中微公司</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>368</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>199.6124</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>373.184</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>-173.5716</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>立讯精密</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>451</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>319</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>197.3741</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>326.7358</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-132</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>-129.3617</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>寒武纪</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>747</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>610</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>308.8124</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>632.4862000000001</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-137</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>-323.6738</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>大族激光</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="n">
+        <v>108.8896</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-153</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>-108.8896</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>建滔积层板</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="n">
+        <v>140.5291</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-153</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>-140.5291</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>京东方A</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="n">
+        <v>60.4539</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-156</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>-60.4539</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>君正股份</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="n">
+        <v>134.0408</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-157</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>-134.0408</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>万华化学</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="n">
+        <v>49.7223</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-159</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>-49.7223</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>德业股份</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="n">
+        <v>55.4717</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-159</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>-55.4717</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>华海清科</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="n">
+        <v>210.239</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-171</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>-210.239</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>亨通光电</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="n">
+        <v>149.5096</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-171</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>-149.5096</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>精测电子</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="n">
+        <v>154.2608</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-175</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>-154.2608</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>中信证券</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n">
+        <v>32.1601</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-181</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>-32.1601</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>华峰测控</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="n">
+        <v>135.2358</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-190</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>-135.2358</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>东山精密</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>621</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>431</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>349.3848</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>667.573</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-190</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>-318.1882</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>中际旭创</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1576</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>961.1922</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>1639.821</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-197</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>-678.6288</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>通信</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>742</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>544</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>228.8814</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>497.6319</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-198</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>-268.7505</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>芯原股份</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="n">
+        <v>139.4115</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-201</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>-139.4115</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>858</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>319.524</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>543.1015</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-222</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>-223.5775</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>回避</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>杰瑞股份</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="n">
+        <v>149.9242</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-239</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>-149.9242</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>华虹宏力</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>464</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>101.7161</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>319.5791</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-246</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>-217.863</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>520</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>102.0876</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>313.2193</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-253</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>-211.1317</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>阳光电源</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="n">
+        <v>116.967</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-271</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>-116.967</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>中国巨石</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="n">
+        <v>168.1703</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-290</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>-168.1703</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>退出前50</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>兆易创新</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>704</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>76.7807</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>467.3359</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-511</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>-390.5552</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>两期在榜</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>低配</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>回避（行业回避或单季减仓≥100家）</t>
         </is>
       </c>
     </row>

--- a/报告/机构持仓决策报告.xlsx
+++ b/报告/机构持仓决策报告.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -555,10 +555,22 @@
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>分歧度数据</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>未就绪：需 fund_industry_50x4.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>结论</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>本期不给「超配/回避」的可执行指令，只给参考清单；原因是超配分位剔 Q4 后 p=0.110、2019–2022 段方向相反（IC −0.055）</t>
         </is>
@@ -575,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -584,9 +596,15 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -637,15 +655,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>加仓基金占比</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>分歧度</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>基金行为</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>理由</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>失效条件</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>证据等级</t>
         </is>
@@ -685,17 +718,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>分位 86%（高位）且主动加仓 +0.49pp</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -735,17 +775,24 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>分位 89%（高位）且主动加仓 +0.09pp</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -785,17 +832,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>分位 95%（高位）且主动加仓 +0.03pp</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -835,17 +889,24 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>分位 27%、主动 +1.60pp，无极端信号</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -885,17 +946,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>分位 57%、主动 +0.68pp，无极端信号</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -935,17 +1003,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>分位 51%、主动 +0.40pp，无极端信号</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -985,17 +1060,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>分位 27%、主动 +0.18pp，无极端信号</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1035,17 +1117,24 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>分位 78%、主动 +0.17pp，无极端信号</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1085,17 +1174,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>分位 38%、主动 +0.17pp，无极端信号</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1135,17 +1231,24 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>分位 49%、主动 +0.03pp，无极端信号</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1185,17 +1288,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>分位 3%</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1235,17 +1345,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>分位 19%</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1285,17 +1402,24 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>分位 19%</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1335,17 +1459,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>分位 0%</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1385,17 +1516,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>分位 11%</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1435,17 +1573,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>分位 0%</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1485,17 +1630,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>分位 16%</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1535,17 +1687,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>分位 3%</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1585,17 +1744,24 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>分位 11%</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1635,17 +1801,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>主动项为负</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1685,17 +1858,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>主动项为负</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1735,17 +1915,24 @@
           <t>极度拥挤</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>主动项为负</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1785,17 +1972,24 @@
           <t>极度拥挤</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>主动项为负</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1835,17 +2029,24 @@
           <t>极度拥挤</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>主动项为负</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1885,17 +2086,24 @@
           <t>极度拥挤</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>主动项为负</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1935,17 +2143,24 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>分位 3%（低位）且主动减仓 -0.00pp</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1985,17 +2200,24 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>分位 16%（低位）且主动减仓 -0.00pp</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2035,17 +2257,24 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>分位 0%（低位）且主动减仓 -0.03pp</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2085,17 +2314,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>分位 0%（低位）且主动减仓 -0.13pp</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2135,17 +2371,24 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>分位 3%（低位）且主动减仓 -0.24pp</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2185,17 +2428,24 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>未采集</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>分位 0%（低位）且主动减仓 -1.37pp</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -5797,7 +6047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6003,30 +6253,62 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>fund_industry</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>基金×申万行业配置（样本）</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50 只偏股混合 × 4 期（2025Q4–2026Q3）</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>全市场 1074 只 × 43 期（逐只查询，约 4.6 万次）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>MCP 单基金查询；已取规模前 50 只做分歧度，样本偏科技主题</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>stock_holdings</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>重仓股持股基金数</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>available</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>每期前 50 只（按持股基金数）</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>批量汇总视图可用；仅前 50、无行业字段</t>
         </is>

--- a/报告/机构持仓决策报告.xlsx
+++ b/报告/机构持仓决策报告.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>未就绪：需 fund_industry_50x4.json</t>
+          <t>真实口径：47 只偏股混合（规模前 50 中有两期数据者）；区间 2025Q4 → 2026Q2（跨两季）；仅前 10 重仓行业、剔除单行业&gt;80% 主题基金，样本偏科技主题</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -670,15 +670,20 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>口径一致性</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>理由</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>失效条件</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>证据等级</t>
         </is>
@@ -718,24 +723,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>共识形成</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>分位 86%（高位）且主动加仓 +0.49pp</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -775,24 +789,33 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.67</v>
+      </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
           <t>分位 89%（高位）且主动加仓 +0.09pp</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -832,24 +855,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.92</v>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>分位 95%（高位）且主动加仓 +0.03pp</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -889,24 +921,33 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0.53</v>
+      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>分位 27%、主动 +1.60pp，无极端信号</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t>分位 27%、主动 +1.60pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +1.60pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 26% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -946,24 +987,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.67</v>
+      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>分位 57%、主动 +0.68pp，无极端信号</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1003,24 +1053,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.37</v>
+      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>分位 51%、主动 +0.40pp，无极端信号</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>分位 51%、主动 +0.40pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.40pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 18% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1060,24 +1119,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>分位 27%、主动 +0.18pp，无极端信号</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
+          <t>分位 27%、主动 +0.18pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.18pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 27% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1117,24 +1185,33 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>分位 78%、主动 +0.17pp，无极端信号</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
+          <t>分位 78%、主动 +0.17pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.17pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 0% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1174,24 +1251,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>分位 38%、主动 +0.17pp，无极端信号</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>分位 38%、主动 +0.17pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.17pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 25% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1231,24 +1317,33 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>分位 49%、主动 +0.03pp，无极端信号</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>分位 49%、主动 +0.03pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.03pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 0% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转负且分位跌破 50%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1288,24 +1383,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.12</v>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>分位 3%</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
+          <t>分位 3%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.31pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 6% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1345,24 +1449,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.8</v>
+      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>分位 19%</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1402,24 +1515,33 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.67</v>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>分位 19%</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
+          <t>分位 19%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.15pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 33% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1459,24 +1581,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>分位 0%</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
+          <t>分位 0%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.14pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 0% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1516,24 +1647,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.55</v>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>分位 11%</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
+          <t>分位 11%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.12pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 28% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1573,24 +1713,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.53</v>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>分位 0%</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
+          <t>分位 0%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.09pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 27% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1630,24 +1779,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.29</v>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>分位 16%</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
+          <t>分位 16%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.06pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 14% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1687,24 +1845,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.17</v>
+      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>分位 3%</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
+          <t>分位 3%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.05pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 8% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1744,24 +1911,33 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.29</v>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>分位 11%</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
+          <t>分位 11%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.02pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 14% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1801,24 +1977,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
           <t>主动项为负</t>
         </is>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1858,24 +2043,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.31</v>
+      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>主动项为负</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1915,24 +2109,33 @@
           <t>极度拥挤</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.54</v>
+      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
           <t>主动项为负</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -1972,24 +2175,33 @@
           <t>极度拥挤</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.89</v>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>主动项为负</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2029,24 +2241,33 @@
           <t>极度拥挤</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.57</v>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>主动项为负</t>
+          <t>冲突（本期减、跨季加）</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
+          <t>主动项为负；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 -0.91pp，但样本基金 2025Q4→2026Q2 有 71% 加仓，需复核</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2086,24 +2307,33 @@
           <t>极度拥挤</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>主动项为负</t>
+          <t>冲突（本期减、跨季加）</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
+          <t>主动项为负；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 -0.92pp，但样本基金 2025Q4→2026Q2 有 72% 加仓，需复核</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2143,24 +2373,33 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
           <t>分位 3%（低位）且主动减仓 -0.00pp</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2200,24 +2439,33 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>分位 16%（低位）且主动减仓 -0.00pp</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2257,24 +2505,33 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
           <t>分位 0%（低位）且主动减仓 -0.03pp</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2314,24 +2571,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.73</v>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
           <t>分位 0%（低位）且主动减仓 -0.13pp</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2371,24 +2637,33 @@
           <t>中性</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.59</v>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
           <t>分位 3%（低位）且主动减仓 -0.24pp</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>
@@ -2428,24 +2703,33 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.61</v>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
           <t>分位 0%（低位）且主动减仓 -1.37pp</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>若下季主动项转正且分位回升至 40% 以上</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>参考（F3e 剔Q4 后 p=0.11；主动项 n=9）</t>
         </is>

--- a/报告/机构持仓决策报告.xlsx
+++ b/报告/机构持仓决策报告.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>真实口径：47 只偏股混合（规模前 50 中有两期数据者）；区间 2025Q4 → 2026Q2（跨两季）；仅前 10 重仓行业、剔除单行业&gt;80% 主题基金，样本偏科技主题</t>
+          <t>真实口径：47 只偏股混合（规模前 50 中有两期数据者）；区间 2026Q2 → 2026Q3（跨两季）；仅前 10 行业、剔除&gt;80% 主题基金、按覆盖率归一化；样本偏科技主题</t>
         </is>
       </c>
     </row>
@@ -724,14 +724,14 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>共识形成</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -790,24 +790,24 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>66.7</v>
+        <v>25</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>分歧</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>分位 89%（高位）且主动加仓 +0.09pp</t>
+          <t>分位 89%（高位）且主动加仓 +0.09pp；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.09pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 25% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -856,24 +856,24 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46.2</v>
+        <v>14.3</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.29</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>多空对撞</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>分位 95%（高位）且主动加仓 +0.03pp</t>
+          <t>分位 95%（高位）且主动加仓 +0.03pp；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.03pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 14% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>26.5</v>
+        <v>25</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
@@ -939,7 +939,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>分位 27%、主动 +1.60pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +1.60pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 26% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 27%、主动 +1.60pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +1.60pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 25% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -988,14 +988,14 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>分歧</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>18.4</v>
+        <v>7.4</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.37</v>
+        <v>0.15</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>分位 51%、主动 +0.40pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.40pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 18% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 51%、主动 +0.40pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.40pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 7% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>26.9</v>
+        <v>20.8</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>分位 27%、主动 +0.18pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.18pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 27% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 27%、主动 +0.18pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.18pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 21% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1186,24 +1186,24 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>系统性撤离</t>
+          <t>共识形成</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>冲突（本期加、跨季减）</t>
+          <t>一致</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>分位 78%、主动 +0.17pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.17pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 0% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 78%、主动 +0.17pp，无极端信号</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1252,14 +1252,14 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>系统性撤离</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>分位 38%、主动 +0.17pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.17pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 25% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 38%、主动 +0.17pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.17pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 33% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>分位 49%、主动 +0.03pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.03pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 0% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 49%、主动 +0.03pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.03pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 0% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0.12</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>分位 3%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.31pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 6% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 3%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.31pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 6% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>40</v>
+        <v>57.1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -1516,14 +1516,14 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>分歧</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>分位 19%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.15pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 33% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 19%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.15pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 25% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1582,24 +1582,24 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>系统性撤离</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>冲突（本期加、跨季减）</t>
+          <t>一致</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>分位 0%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.14pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 0% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 0%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>27.5</v>
+        <v>14.3</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.55</v>
+        <v>0.29</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>分位 11%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.12pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 28% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 11%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.12pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 14% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>26.7</v>
+        <v>12.5</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>分位 0%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.09pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 27% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 0%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.09pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 12% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>分位 16%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.06pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 14% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 16%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.06pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 0% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1846,14 +1846,14 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.17</v>
+        <v>0.67</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>系统性撤离</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>分位 3%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.05pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 8% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 3%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.05pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 33% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>分位 11%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.02pp（全市场单季），但样本基金 2025Q4→2026Q2 仅 14% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 11%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.02pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 17% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -1977,20 +1977,16 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>系统性撤离</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>未采集</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2044,10 +2040,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
@@ -2110,24 +2106,24 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>26.8</v>
+        <v>70</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.54</v>
+        <v>0.6</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>系统性撤离</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>冲突（本期减、跨季加）</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>主动项为负</t>
+          <t>主动项为负；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 -0.42pp，但样本基金 2026Q2→2026Q3 有 70% 加仓，需复核</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2176,14 +2172,14 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>55.3</v>
+        <v>20.9</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.89</v>
+        <v>0.42</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>多空对撞</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -2242,24 +2238,24 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>21.1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.57</v>
+        <v>0.42</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>分歧</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>冲突（本期减、跨季加）</t>
+          <t>一致</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>主动项为负；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 -0.91pp，但样本基金 2025Q4→2026Q2 有 71% 加仓，需复核</t>
+          <t>主动项为负</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2308,24 +2304,24 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>48.7</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>分歧</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>冲突（本期减、跨季加）</t>
+          <t>一致</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>主动项为负；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 -0.92pp，但样本基金 2025Q4→2026Q2 有 72% 加仓，需复核</t>
+          <t>主动项为负</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2374,14 +2370,14 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>系统性撤离</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2440,10 +2436,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -2506,14 +2502,14 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>多空对撞</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -2572,14 +2568,14 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>36.6</v>
+        <v>7.7</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.73</v>
+        <v>0.15</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>分歧</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -2638,10 +2634,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>29.3</v>
+        <v>2.9</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.59</v>
+        <v>0.06</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -2704,14 +2700,14 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>30.4</v>
+        <v>11.4</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.61</v>
+        <v>0.23</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>分歧</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -6735,7 +6731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6850,6 +6846,18 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>分歧度归一化</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>季报期由前十大推导（覆盖约 60%），半年报/年报用全持仓表（约 88%）：先除以每只基金每期覆盖率再比较；不归一化会把覆盖率下降误算成全面减仓（电子原始 3 加/39 减，归一化后 19 加/19 减）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/报告/机构持仓决策报告.xlsx
+++ b/报告/机构持仓决策报告.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 数据健康" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 反证清单" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 口径说明" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 数据源交叉验证" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -560,7 +561,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>真实口径：47 只偏股混合（规模前 50 中有两期数据者）；区间 2026Q2 → 2026Q3（跨两季）；仅前 10 行业、剔除&gt;80% 主题基金、按覆盖率归一化；样本偏科技主题</t>
+          <t>真实口径：47 只偏股混合（规模前 50 中有两期数据者）；区间 2026Q2 → 2026Q3；样本最多 375 只，按覆盖率归一化，剔除&gt;80% 主题基金；来源 东方财富（AKShare）全市场</t>
         </is>
       </c>
     </row>
@@ -724,24 +725,24 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>50</v>
+        <v>36.9</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>多空对撞</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>分位 86%（高位）且主动加仓 +0.49pp</t>
+          <t>分位 86%（高位）且主动加仓 +0.49pp；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.49pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 37% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -790,10 +791,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
@@ -807,7 +808,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>分位 89%（高位）且主动加仓 +0.09pp；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.09pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 25% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 89%（高位）且主动加仓 +0.09pp；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.09pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 24% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -856,10 +857,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14.3</v>
+        <v>25.9</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.29</v>
+        <v>0.52</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
@@ -873,7 +874,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>分位 95%（高位）且主动加仓 +0.03pp；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.03pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 14% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 95%（高位）且主动加仓 +0.03pp；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.03pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 26% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -922,24 +923,24 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>25</v>
+        <v>42.5</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>系统性撤离</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>冲突（本期加、跨季减）</t>
+          <t>一致</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>分位 27%、主动 +1.60pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +1.60pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 25% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 27%、主动 +1.60pp，无极端信号</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -988,10 +989,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>50</v>
+        <v>56.3</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
@@ -1054,10 +1055,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7.4</v>
+        <v>29.4</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.15</v>
+        <v>0.59</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
@@ -1071,7 +1072,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>分位 51%、主动 +0.40pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.40pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 7% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 51%、主动 +0.40pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.40pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 29% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1120,10 +1121,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>20.8</v>
+        <v>19.2</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
@@ -1137,7 +1138,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>分位 27%、主动 +0.18pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.18pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 21% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 27%、主动 +0.18pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.18pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 19% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1186,24 +1187,24 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>共识形成</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>分位 78%、主动 +0.17pp，无极端信号</t>
+          <t>分位 78%、主动 +0.17pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.17pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 35% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1252,14 +1253,14 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>33.3</v>
+        <v>28.4</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>分歧</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1269,7 +1270,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>分位 38%、主动 +0.17pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.17pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 33% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 38%、主动 +0.17pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.17pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 28% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1318,10 +1319,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
@@ -1335,7 +1336,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>分位 49%、主动 +0.03pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.03pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 0% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 49%、主动 +0.03pp，无极端信号；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.03pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 24% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1384,10 +1385,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6.2</v>
+        <v>20.3</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.12</v>
+        <v>0.41</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
@@ -1401,7 +1402,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>分位 3%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.31pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 6% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 3%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.31pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 20% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1450,10 +1451,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>57.1</v>
+        <v>41.7</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
@@ -1516,10 +1517,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
@@ -1533,7 +1534,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>分位 19%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.15pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 25% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 19%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.15pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 22% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1582,24 +1583,24 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>多空对撞</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>冲突（本期加、跨季减）</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>分位 0%</t>
+          <t>分位 0%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.14pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 34% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1648,10 +1649,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>14.3</v>
+        <v>22.9</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.29</v>
+        <v>0.46</v>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
@@ -1665,7 +1666,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>分位 11%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.12pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 14% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 11%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.12pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 23% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1714,10 +1715,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>12.5</v>
+        <v>16.7</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
@@ -1731,7 +1732,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>分位 0%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.09pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 12% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 0%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.09pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 17% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1780,10 +1781,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
@@ -1797,7 +1798,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>分位 16%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.06pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 0% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 16%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.06pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 27% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1846,14 +1847,14 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>33.3</v>
+        <v>25.4</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.67</v>
+        <v>0.51</v>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>分歧</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1863,7 +1864,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>分位 3%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.05pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 33% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
+          <t>分位 3%；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 +0.05pp（全市场单季），但样本基金 2026Q2→2026Q3 仅 25% 加仓——可能是跨期反弹，也可能样本偏差，下季需用同口径复核</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -1912,10 +1913,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>16.7</v>
+        <v>17.3</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
@@ -1977,16 +1978,20 @@
           <t>显著低配</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.3</v>
+      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>未采集</t>
+          <t>一致</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2040,14 +2045,14 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>系统性撤离</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2106,24 +2111,24 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>70</v>
+        <v>46.8</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.6</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>分歧</t>
+          <t>多空对撞</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>冲突（本期减、跨季加）</t>
+          <t>一致</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>主动项为负；&lt;b&gt;口径冲突&lt;/b&gt;：2026Q3 主动 -0.42pp，但样本基金 2026Q2→2026Q3 有 70% 加仓，需复核</t>
+          <t>主动项为负</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2172,10 +2177,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>20.9</v>
+        <v>26.9</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
@@ -2238,10 +2243,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
@@ -2304,14 +2309,14 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>48.7</v>
+        <v>33.3</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.97</v>
+        <v>0.67</v>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>多空对撞</t>
+          <t>分歧</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -2370,14 +2375,14 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>50</v>
+        <v>19.5</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>多空对撞</t>
+          <t>系统性撤离</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -2436,10 +2441,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
@@ -2502,10 +2507,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
@@ -2568,10 +2573,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7.7</v>
+        <v>29.9</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
@@ -2634,10 +2639,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.9</v>
+        <v>21.9</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.06</v>
+        <v>0.44</v>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
@@ -2700,10 +2705,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>11.4</v>
+        <v>29.6</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -6861,4 +6866,234 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>行业</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>平均绝对偏差</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Wind均值</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>东财均值</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>相关</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>医药生物</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.888</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>通信</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.961</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>电子</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.981</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>建筑材料</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.973</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>电力设备</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.988</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>机械设备</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.986</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>国防军工</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>